--- a/PLTR_Model.xlsx
+++ b/PLTR_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49FDEEA-EBD7-449C-AC2C-95EAB62DEEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBCA8E8-86CE-464E-A352-337401F4303B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3688,11 +3688,11 @@
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="4" builtinId="3"/>
@@ -11060,8 +11060,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="207818" y="6286500"/>
-          <a:ext cx="5466434" cy="4866409"/>
+          <a:off x="214313" y="6858000"/>
+          <a:ext cx="5583332" cy="5351318"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11207,7 +11207,7 @@
       <xdr:col>59</xdr:col>
       <xdr:colOff>8785</xdr:colOff>
       <xdr:row>99</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:rowOff>6111</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -13810,34 +13810,34 @@
         <f t="shared" si="7"/>
         <v>0.28422577042500707</v>
       </c>
-      <c r="AN8" s="80">
+      <c r="AN8" s="79">
         <v>0.51</v>
       </c>
-      <c r="AO8" s="80">
+      <c r="AO8" s="79">
         <v>0.46</v>
       </c>
-      <c r="AP8" s="80">
+      <c r="AP8" s="79">
         <v>0.43</v>
       </c>
-      <c r="AQ8" s="80">
+      <c r="AQ8" s="79">
         <v>0.38</v>
       </c>
-      <c r="AR8" s="80">
+      <c r="AR8" s="79">
         <v>0.32</v>
       </c>
-      <c r="AS8" s="80">
+      <c r="AS8" s="79">
         <v>0.26</v>
       </c>
-      <c r="AT8" s="80">
+      <c r="AT8" s="79">
         <v>0.2</v>
       </c>
-      <c r="AU8" s="80">
+      <c r="AU8" s="79">
         <v>0.15</v>
       </c>
-      <c r="AV8" s="80">
+      <c r="AV8" s="79">
         <v>0.11</v>
       </c>
-      <c r="AW8" s="80">
+      <c r="AW8" s="79">
         <v>0.06</v>
       </c>
     </row>
@@ -13941,34 +13941,34 @@
         <f t="shared" si="7"/>
         <v>0.29228547751937839</v>
       </c>
-      <c r="AN9" s="80">
+      <c r="AN9" s="79">
         <v>0.56000000000000005</v>
       </c>
-      <c r="AO9" s="80">
+      <c r="AO9" s="79">
         <v>0.38</v>
       </c>
-      <c r="AP9" s="80">
+      <c r="AP9" s="79">
         <v>0.32</v>
       </c>
-      <c r="AQ9" s="80">
+      <c r="AQ9" s="79">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AR9" s="80">
+      <c r="AR9" s="79">
         <v>0.26</v>
       </c>
-      <c r="AS9" s="80">
+      <c r="AS9" s="79">
         <v>0.2</v>
       </c>
-      <c r="AT9" s="80">
+      <c r="AT9" s="79">
         <v>0.2</v>
       </c>
-      <c r="AU9" s="80">
+      <c r="AU9" s="79">
         <v>0.2</v>
       </c>
-      <c r="AV9" s="80">
+      <c r="AV9" s="79">
         <v>0.2</v>
       </c>
-      <c r="AW9" s="80">
+      <c r="AW9" s="79">
         <v>0.2</v>
       </c>
     </row>
@@ -14077,43 +14077,43 @@
         <f t="shared" si="7"/>
         <v>0.28785822278711293</v>
       </c>
-      <c r="AN10" s="81">
+      <c r="AN10" s="80">
         <f t="shared" ref="AN10:AW10" si="9">AN6/AM6-1</f>
         <v>0.53261210957948024</v>
       </c>
-      <c r="AO10" s="81">
+      <c r="AO10" s="80">
         <f t="shared" si="9"/>
         <v>0.4231740965912969</v>
       </c>
-      <c r="AP10" s="81">
+      <c r="AP10" s="80">
         <f t="shared" si="9"/>
         <v>0.3809004893460477</v>
       </c>
-      <c r="AQ10" s="81">
+      <c r="AQ10" s="80">
         <f t="shared" si="9"/>
         <v>0.34159935352663906</v>
       </c>
-      <c r="AR10" s="81">
+      <c r="AR10" s="80">
         <f t="shared" si="9"/>
         <v>0.29538418911705722</v>
       </c>
-      <c r="AS10" s="81">
+      <c r="AS10" s="80">
         <f t="shared" si="9"/>
         <v>0.23605658462324675</v>
       </c>
-      <c r="AT10" s="81">
+      <c r="AT10" s="80">
         <f t="shared" si="9"/>
         <v>0.20000000000000018</v>
       </c>
-      <c r="AU10" s="81">
+      <c r="AU10" s="80">
         <f t="shared" si="9"/>
         <v>0.16937080848450892</v>
       </c>
-      <c r="AV10" s="81">
+      <c r="AV10" s="80">
         <f t="shared" si="9"/>
         <v>0.14578073441115302</v>
       </c>
-      <c r="AW10" s="81">
+      <c r="AW10" s="80">
         <f t="shared" si="9"/>
         <v>0.11829274504993093</v>
       </c>
@@ -20704,11 +20704,11 @@
       <c r="AS66" s="54"/>
       <c r="AT66" s="54"/>
       <c r="AU66" s="54"/>
-      <c r="AV66" s="79" t="str" cm="1">
+      <c r="AV66" s="81" t="str" cm="1">
         <f t="array" ref="AV66">_xlfn.IFS(AW65&gt;=25%,"Strong Buy",AW65&gt;=10.00001%,"Buy",AND(AW65&lt;=10%,AW65&gt;=-4.9999%),"Hold",AND(AW65&lt;=-5%,AW65&gt;=-14.999999%),"Sell",AW65&lt;=-15%,"Strong Sell")</f>
         <v>Buy</v>
       </c>
-      <c r="AW66" s="79"/>
+      <c r="AW66" s="81"/>
     </row>
     <row r="67" spans="2:101" ht="14.25" customHeight="1">
       <c r="B67" s="1" t="s">

--- a/PLTR_Model.xlsx
+++ b/PLTR_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBCA8E8-86CE-464E-A352-337401F4303B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF68CF60-46C5-4561-85FA-3653398A3F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
